--- a/data/trans_dic/P45C_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,88; 27,62</t>
+          <t>20,29; 28,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 36,2</t>
+          <t>27,73; 36,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,11; 28,84</t>
+          <t>20,04; 28,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,57; 28,92</t>
+          <t>14,59; 29,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,11; 30,98</t>
+          <t>23,28; 31,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,94; 34,55</t>
+          <t>25,97; 34,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,63; 29,27</t>
+          <t>20,44; 28,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 28,82</t>
+          <t>16,26; 28,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,58; 28,23</t>
+          <t>22,84; 28,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 34,04</t>
+          <t>27,82; 33,9</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,73; 27,64</t>
+          <t>21,48; 27,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 26,4</t>
+          <t>17,05; 27,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,13; 24,2</t>
+          <t>18,36; 24,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,45; 28,34</t>
+          <t>21,77; 28,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,81; 22,22</t>
+          <t>15,43; 21,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,76; 31,91</t>
+          <t>20,85; 31,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,37; 21,46</t>
+          <t>15,65; 21,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 17,68</t>
+          <t>11,85; 17,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,75; 25,6</t>
+          <t>19,08; 25,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,88; 22,31</t>
+          <t>10,32; 22,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 22,18</t>
+          <t>17,78; 22,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 22,11</t>
+          <t>17,65; 22,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 23,11</t>
+          <t>17,96; 22,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,59; 25,17</t>
+          <t>16,15; 25,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 17,68</t>
+          <t>11,99; 17,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 19,37</t>
+          <t>13,7; 19,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,86</t>
+          <t>9,79; 14,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,46; 24,47</t>
+          <t>17,28; 24,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,86</t>
+          <t>9,2; 14,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 18,22</t>
+          <t>12,6; 18,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,13; 16,3</t>
+          <t>10,95; 16,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 18,39</t>
+          <t>13,38; 18,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 14,87</t>
+          <t>11,33; 15,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,98; 17,86</t>
+          <t>14,07; 18,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,01; 14,61</t>
+          <t>11,23; 15,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,07; 20,52</t>
+          <t>16,2; 20,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 19,34</t>
+          <t>12,97; 19,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 19,86</t>
+          <t>13,69; 19,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 14,99</t>
+          <t>9,85; 14,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,28</t>
+          <t>5,04; 16,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,57</t>
+          <t>7,52; 12,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,55</t>
+          <t>9,08; 14,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,73</t>
+          <t>8,81; 14,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 15,58</t>
+          <t>10,7; 15,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 15,26</t>
+          <t>10,89; 15,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,12</t>
+          <t>12,21; 16,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,58</t>
+          <t>9,96; 13,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 14,88</t>
+          <t>6,91; 14,88</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 13,02</t>
+          <t>7,01; 12,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 13,06</t>
+          <t>7,59; 13,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 13,66</t>
+          <t>7,98; 13,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 16,13</t>
+          <t>10,77; 16,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,99</t>
+          <t>4,46; 9,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,4</t>
+          <t>6,89; 12,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 13,75</t>
+          <t>7,79; 13,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,93</t>
+          <t>9,55; 13,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,35</t>
+          <t>6,55; 10,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,69</t>
+          <t>7,85; 11,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,58</t>
+          <t>8,72; 12,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,87; 14,33</t>
+          <t>10,95; 14,34</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,2</t>
+          <t>3,08; 8,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,46</t>
+          <t>4,53; 10,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,82</t>
+          <t>4,11; 9,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,02; 11,83</t>
+          <t>7,03; 12,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,14</t>
+          <t>2,57; 6,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,63</t>
+          <t>3,6; 9,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,76</t>
+          <t>5,34; 11,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,59</t>
+          <t>1,59; 7,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,55</t>
+          <t>3,31; 6,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,61</t>
+          <t>4,68; 8,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,2</t>
+          <t>5,18; 9,16</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,39</t>
+          <t>3,12; 8,46</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,91</t>
+          <t>3,06; 9,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,19</t>
+          <t>1,29; 6,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,57</t>
+          <t>2,57; 7,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 10,38</t>
+          <t>5,25; 9,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,49</t>
+          <t>0,37; 3,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,45</t>
+          <t>2,8; 7,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,28</t>
+          <t>1,94; 6,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,19</t>
+          <t>3,5; 6,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,18</t>
+          <t>1,75; 4,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,78</t>
+          <t>2,63; 5,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,82</t>
+          <t>2,61; 5,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,22</t>
+          <t>4,65; 7,24</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,93</t>
+          <t>14,42; 17,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,3; 18,91</t>
+          <t>16,22; 18,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,88</t>
+          <t>12,22; 14,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,27</t>
+          <t>12,05; 17,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,53</t>
+          <t>11,4; 13,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,66</t>
+          <t>12,26; 14,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,43; 14,69</t>
+          <t>12,39; 14,7</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 13,69</t>
+          <t>10,05; 13,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,16; 14,92</t>
+          <t>13,15; 14,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,67; 16,4</t>
+          <t>14,62; 16,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,65; 14,43</t>
+          <t>12,73; 14,33</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,04; 15,0</t>
+          <t>11,95; 15,06</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97859; 135989</t>
+          <t>99891; 137946</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123037; 163128</t>
+          <t>124954; 163515</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83434; 119652</t>
+          <t>83140; 118111</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58283; 115671</t>
+          <t>58356; 116165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>107620; 144266</t>
+          <t>108401; 146632</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>110521; 147211</t>
+          <t>110655; 148435</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81427; 115527</t>
+          <t>80700; 113043</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50454; 90272</t>
+          <t>50933; 88932</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216291; 270502</t>
+          <t>218788; 273052</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>246564; 298394</t>
+          <t>243902; 297197</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175924; 223749</t>
+          <t>173868; 223396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>122158; 188286</t>
+          <t>121592; 193876</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>133015; 177534</t>
+          <t>134722; 179143</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146342; 193372</t>
+          <t>148534; 193243</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92535; 130068</t>
+          <t>90319; 128544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87949; 135158</t>
+          <t>88307; 134080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>95972; 133957</t>
+          <t>97730; 136150</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72280; 107564</t>
+          <t>72104; 108126</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>105500; 144031</t>
+          <t>107361; 145626</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55648; 114086</t>
+          <t>52754; 112735</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>241379; 301123</t>
+          <t>241399; 302419</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>227940; 285307</t>
+          <t>227828; 287609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210726; 265325</t>
+          <t>206207; 259940</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>155137; 235310</t>
+          <t>151028; 236521</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77945; 112792</t>
+          <t>76474; 112771</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92772; 131529</t>
+          <t>93037; 134469</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65269; 99011</t>
+          <t>65178; 98906</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92962; 130312</t>
+          <t>92023; 132373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>62854; 95438</t>
+          <t>63341; 96697</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87984; 128327</t>
+          <t>88791; 128406</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>73102; 107079</t>
+          <t>71946; 106089</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>71819; 99769</t>
+          <t>72598; 99797</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>148580; 197319</t>
+          <t>150369; 200824</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>193391; 247127</t>
+          <t>194638; 250914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145672; 193273</t>
+          <t>148551; 198830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>172721; 220648</t>
+          <t>174138; 220773</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65854; 100164</t>
+          <t>67198; 101323</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84293; 120793</t>
+          <t>83299; 119461</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62018; 96392</t>
+          <t>63326; 95301</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41872; 144353</t>
+          <t>44665; 148151</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37751; 64572</t>
+          <t>38647; 64236</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55784; 89050</t>
+          <t>55544; 88943</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56422; 88223</t>
+          <t>56627; 90505</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78415; 110806</t>
+          <t>76124; 109573</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111608; 157397</t>
+          <t>112314; 155945</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>147553; 196700</t>
+          <t>149013; 198522</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125896; 174580</t>
+          <t>128018; 174845</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>116337; 237726</t>
+          <t>110420; 237777</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26596; 50198</t>
+          <t>27047; 49111</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31492; 55792</t>
+          <t>32428; 57257</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36566; 64806</t>
+          <t>37850; 65452</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60901; 90361</t>
+          <t>60318; 90297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19339; 40375</t>
+          <t>18022; 39209</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29896; 55266</t>
+          <t>30692; 55579</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38565; 67819</t>
+          <t>38401; 67447</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>53150; 76233</t>
+          <t>52283; 75259</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52005; 81720</t>
+          <t>51740; 81586</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66471; 102052</t>
+          <t>68541; 103507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83278; 121771</t>
+          <t>84411; 123108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>120350; 158714</t>
+          <t>121235; 158826</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8542; 23911</t>
+          <t>8965; 24665</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13885; 32108</t>
+          <t>13913; 32509</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13549; 32366</t>
+          <t>13545; 32781</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25765; 43446</t>
+          <t>25799; 44282</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8601; 24501</t>
+          <t>8814; 23385</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12688; 30134</t>
+          <t>12551; 31661</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18692; 40107</t>
+          <t>19922; 41830</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10795; 46153</t>
+          <t>9687; 46214</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21394; 41567</t>
+          <t>20997; 42214</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31768; 56497</t>
+          <t>30671; 56033</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36986; 64590</t>
+          <t>36351; 64356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29548; 81780</t>
+          <t>30407; 82508</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6666; 20794</t>
+          <t>6414; 20113</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3204; 15138</t>
+          <t>3147; 14824</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5977; 19107</t>
+          <t>6472; 19814</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15258; 29310</t>
+          <t>14821; 28038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1177; 11561</t>
+          <t>1225; 11419</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9970; 28169</t>
+          <t>10567; 27533</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7542; 24841</t>
+          <t>7673; 23918</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14598; 26376</t>
+          <t>14897; 27044</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9834; 28065</t>
+          <t>9467; 26273</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16130; 35981</t>
+          <t>16387; 36541</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16592; 37700</t>
+          <t>16933; 38752</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32968; 51139</t>
+          <t>32898; 51263</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>470835; 553488</t>
+          <t>471293; 558570</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>553901; 642646</t>
+          <t>551193; 641753</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>417035; 500918</t>
+          <t>411298; 496714</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>427918; 596289</t>
+          <t>415959; 602016</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>380482; 456084</t>
+          <t>384174; 457603</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>430882; 516401</t>
+          <t>431953; 515392</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>437175; 516935</t>
+          <t>436026; 517030</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>371769; 501114</t>
+          <t>367559; 499047</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>873613; 990516</t>
+          <t>873195; 991115</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1015275; 1135391</t>
+          <t>1012265; 1136203</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>870594; 993009</t>
+          <t>876401; 986589</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>856184; 1066815</t>
+          <t>850031; 1071214</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,29; 28,02</t>
+          <t>20,27; 27,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,73; 36,28</t>
+          <t>27,71; 36,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,04; 28,47</t>
+          <t>20,15; 28,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,59; 29,04</t>
+          <t>15,01; 27,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,28; 31,49</t>
+          <t>23,05; 30,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,97; 34,84</t>
+          <t>25,85; 34,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,44; 28,64</t>
+          <t>20,52; 28,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 28,39</t>
+          <t>15,81; 27,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,84; 28,5</t>
+          <t>22,86; 28,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,82; 33,9</t>
+          <t>27,58; 34,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,48; 27,6</t>
+          <t>21,23; 27,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 27,18</t>
+          <t>17,01; 25,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,36; 24,42</t>
+          <t>18,28; 24,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,77; 28,32</t>
+          <t>21,29; 28,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,43; 21,96</t>
+          <t>15,79; 22,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,85; 31,66</t>
+          <t>21,7; 33,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,65; 21,81</t>
+          <t>15,51; 21,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 17,77</t>
+          <t>12,04; 18,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,08; 25,88</t>
+          <t>19,03; 25,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,32; 22,05</t>
+          <t>15,73; 23,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 22,27</t>
+          <t>17,71; 21,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,65; 22,28</t>
+          <t>17,97; 22,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 22,65</t>
+          <t>18,2; 22,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,15; 25,3</t>
+          <t>20,03; 26,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,99; 17,68</t>
+          <t>12,1; 17,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,7; 19,8</t>
+          <t>13,54; 19,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,85</t>
+          <t>9,92; 15,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,28; 24,85</t>
+          <t>17,34; 24,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,04</t>
+          <t>9,43; 14,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,6; 18,23</t>
+          <t>12,8; 18,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,95; 16,15</t>
+          <t>10,75; 15,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 18,4</t>
+          <t>12,88; 18,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,14</t>
+          <t>11,07; 14,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 18,14</t>
+          <t>13,85; 18,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,03</t>
+          <t>11,17; 14,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,2; 20,54</t>
+          <t>16,06; 20,49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,97; 19,56</t>
+          <t>13,19; 19,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 19,64</t>
+          <t>13,92; 19,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,82</t>
+          <t>9,63; 15,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 16,71</t>
+          <t>13,05; 18,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,51</t>
+          <t>7,54; 12,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 14,53</t>
+          <t>9,19; 14,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 14,08</t>
+          <t>8,92; 14,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 15,41</t>
+          <t>11,88; 16,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 15,12</t>
+          <t>10,87; 15,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 16,27</t>
+          <t>12,13; 16,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 13,6</t>
+          <t>10,11; 13,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,88</t>
+          <t>12,96; 16,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 12,73</t>
+          <t>6,82; 12,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,4</t>
+          <t>7,46; 13,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 13,8</t>
+          <t>7,87; 13,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,77; 16,12</t>
+          <t>10,63; 15,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,71</t>
+          <t>4,89; 9,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 12,47</t>
+          <t>6,89; 12,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 13,67</t>
+          <t>7,89; 13,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 13,75</t>
+          <t>9,82; 13,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,33</t>
+          <t>6,36; 10,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 11,86</t>
+          <t>7,88; 11,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,72</t>
+          <t>8,56; 12,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 14,34</t>
+          <t>11,04; 14,4</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,46</t>
+          <t>3,1; 8,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,59</t>
+          <t>4,99; 11,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,95</t>
+          <t>4,07; 9,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,06</t>
+          <t>7,64; 12,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,82</t>
+          <t>2,45; 6,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,07</t>
+          <t>3,36; 8,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,22</t>
+          <t>5,33; 11,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,6</t>
+          <t>5,28; 8,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,65</t>
+          <t>3,35; 6,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,54</t>
+          <t>4,8; 8,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,16</t>
+          <t>5,31; 9,29</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,46</t>
+          <t>6,93; 10,1</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,58</t>
+          <t>3,13; 9,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,06</t>
+          <t>1,3; 6,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,85</t>
+          <t>2,55; 8,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 9,93</t>
+          <t>5,62; 10,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,44</t>
+          <t>0,35; 3,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 7,28</t>
+          <t>2,84; 7,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,05</t>
+          <t>1,97; 5,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,35</t>
+          <t>3,41; 6,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,85</t>
+          <t>1,81; 4,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,87</t>
+          <t>2,73; 5,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,98</t>
+          <t>2,59; 5,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,24</t>
+          <t>4,62; 7,15</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,42; 17,09</t>
+          <t>14,45; 17,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,22; 18,88</t>
+          <t>16,22; 18,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,22; 14,76</t>
+          <t>12,24; 14,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,44</t>
+          <t>15,51; 18,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,57</t>
+          <t>11,29; 13,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,26; 14,63</t>
+          <t>12,43; 14,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,7</t>
+          <t>12,43; 14,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,05; 13,64</t>
+          <t>12,32; 14,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,15; 14,93</t>
+          <t>13,26; 14,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14,62; 16,41</t>
+          <t>14,62; 16,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12,73; 14,33</t>
+          <t>12,73; 14,4</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,95; 15,06</t>
+          <t>14,26; 16,07</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83301</t>
+          <t>87907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68905</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>152207</t>
+          <t>164483</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99891; 137946</t>
+          <t>99826; 136480</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>124954; 163515</t>
+          <t>124864; 163082</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83140; 118111</t>
+          <t>83605; 119033</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58356; 116165</t>
+          <t>61195; 113294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>108401; 146632</t>
+          <t>107349; 144138</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>110655; 148435</t>
+          <t>110131; 147710</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80700; 113043</t>
+          <t>81011; 112837</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50933; 88932</t>
+          <t>57308; 99109</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>218788; 273052</t>
+          <t>218999; 270499</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>243902; 297197</t>
+          <t>241834; 299023</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173868; 223396</t>
+          <t>171846; 221548</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>121592; 193876</t>
+          <t>131064; 198049</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110044</t>
+          <t>127312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89988</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>200032</t>
+          <t>224446</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>134722; 179143</t>
+          <t>134116; 178780</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148534; 193243</t>
+          <t>145299; 191300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90319; 128544</t>
+          <t>92434; 130590</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88307; 134080</t>
+          <t>103492; 159168</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>97730; 136150</t>
+          <t>96824; 136419</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72104; 108126</t>
+          <t>73214; 109644</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>107361; 145626</t>
+          <t>107062; 145118</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52754; 112735</t>
+          <t>78599; 116511</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>241399; 302419</t>
+          <t>240479; 298022</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>227828; 287609</t>
+          <t>231948; 293447</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>206207; 259940</t>
+          <t>208941; 263162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>151028; 236521</t>
+          <t>195570; 259408</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>127946</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85184</t>
+          <t>97380</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>196386</t>
+          <t>225326</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76474; 112771</t>
+          <t>77169; 112324</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93037; 134469</t>
+          <t>91938; 131961</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65178; 98906</t>
+          <t>66081; 100015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92023; 132373</t>
+          <t>106975; 151074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63341; 96697</t>
+          <t>64941; 98075</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88791; 128406</t>
+          <t>90193; 129610</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71946; 106089</t>
+          <t>70607; 104557</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72598; 99797</t>
+          <t>80159; 112786</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150369; 200824</t>
+          <t>146859; 197495</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194638; 250914</t>
+          <t>191662; 249665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148551; 198830</t>
+          <t>147821; 195627</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>174138; 220773</t>
+          <t>198989; 253860</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98490</t>
+          <t>110068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94722</t>
+          <t>102451</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>212519</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>67198; 101323</t>
+          <t>68330; 102188</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83299; 119461</t>
+          <t>84651; 121520</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63326; 95301</t>
+          <t>61912; 96511</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44665; 148151</t>
+          <t>91306; 132313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38647; 64236</t>
+          <t>38731; 66177</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55544; 88943</t>
+          <t>56225; 89324</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56627; 90505</t>
+          <t>57320; 90037</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>76124; 109573</t>
+          <t>87310; 117611</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112314; 155945</t>
+          <t>112104; 156358</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>149013; 198522</t>
+          <t>148067; 198795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>128018; 174845</t>
+          <t>130004; 174968</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>110420; 237777</t>
+          <t>185831; 235615</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>81012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63540</t>
+          <t>71769</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>137981</t>
+          <t>152780</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>27047; 49111</t>
+          <t>26294; 48458</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32428; 57257</t>
+          <t>31887; 56569</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37850; 65452</t>
+          <t>37325; 65916</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60318; 90297</t>
+          <t>64659; 96371</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18022; 39209</t>
+          <t>19735; 39929</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30692; 55579</t>
+          <t>30692; 55088</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38401; 67447</t>
+          <t>38892; 68589</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52283; 75259</t>
+          <t>59743; 83690</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51740; 81586</t>
+          <t>50259; 81606</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68541; 103507</t>
+          <t>68819; 102830</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84411; 123108</t>
+          <t>82879; 123184</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>121235; 158826</t>
+          <t>134294; 175210</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>30290</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61469</t>
+          <t>70544</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8965; 24665</t>
+          <t>9034; 25135</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13913; 32509</t>
+          <t>15311; 34011</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13545; 32781</t>
+          <t>13399; 31111</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25799; 44282</t>
+          <t>31002; 51629</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8814; 23385</t>
+          <t>8388; 23444</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12551; 31661</t>
+          <t>11740; 30989</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19922; 41830</t>
+          <t>19853; 41212</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9687; 46214</t>
+          <t>23163; 38221</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20997; 42214</t>
+          <t>21253; 42180</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30671; 56033</t>
+          <t>31500; 58452</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36351; 64356</t>
+          <t>37317; 65220</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30407; 82508</t>
+          <t>58494; 85313</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>45490</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6414; 20113</t>
+          <t>6579; 20491</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3147; 14824</t>
+          <t>3173; 14865</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6472; 19814</t>
+          <t>6441; 20420</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14821; 28038</t>
+          <t>17424; 32388</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1225; 11419</t>
+          <t>1167; 10510</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10567; 27533</t>
+          <t>10722; 26895</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7673; 23918</t>
+          <t>7774; 23396</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14897; 27044</t>
+          <t>15835; 29862</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9467; 26273</t>
+          <t>9792; 25882</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16387; 36541</t>
+          <t>16984; 36846</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16933; 38752</t>
+          <t>16767; 37878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32898; 51263</t>
+          <t>35802; 55367</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>450443</t>
+          <t>497389</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>982460</t>
+          <t>1095588</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>471293; 558570</t>
+          <t>472239; 557285</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>551193; 641753</t>
+          <t>551494; 643560</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>411298; 496714</t>
+          <t>411999; 493086</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>415959; 602016</t>
+          <t>546737; 656550</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>384174; 457603</t>
+          <t>380718; 459893</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>431953; 515392</t>
+          <t>438102; 517413</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>436026; 517030</t>
+          <t>437319; 520957</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>367559; 499047</t>
+          <t>459725; 538703</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>873195; 991115</t>
+          <t>880119; 988972</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1012265; 1136203</t>
+          <t>1012196; 1131831</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>876401; 986589</t>
+          <t>876199; 990913</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>850031; 1071214</t>
+          <t>1034481; 1166270</t>
         </is>
       </c>
     </row>
